--- a/XmlData/Datas/__tables__.xlsx
+++ b/XmlData/Datas/__tables__.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace2\luban_examples\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yinya\Documents\unityProjects\GGJ2026\XmlData\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C3A7ABB-0FC0-44C9-B805-C6CF73A19780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCAB9371-EAEE-4DE4-BD2B-DAC07DB7AFC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
   <si>
     <t>##var</t>
   </si>
@@ -101,30 +101,48 @@
   </si>
   <si>
     <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
+  </si>
+  <si>
+    <t>Table.TbCheeseDictionary</t>
+  </si>
+  <si>
+    <t>CheeseDictionary.xlsx</t>
+  </si>
+  <si>
+    <t>Table.TbCheeseScene</t>
+  </si>
+  <si>
+    <t>Data.CheeseScene</t>
+  </si>
+  <si>
+    <t>CheeseScene.xlsx</t>
+  </si>
+  <si>
+    <t>Data.CheeseDictionary</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -169,8 +187,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="好" xfId="1" builtinId="26"/>
+    <cellStyle name="Good" xfId="1" builtinId="26"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -443,17 +461,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="20.375" customWidth="1"/>
-    <col min="3" max="3" width="15.625" customWidth="1"/>
-    <col min="4" max="4" width="32.375" customWidth="1"/>
-    <col min="5" max="5" width="24.375" customWidth="1"/>
-    <col min="6" max="9" width="18" customWidth="1"/>
+    <col min="1" max="1" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="58.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="98.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="64.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="33.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -488,7 +512,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" s="1" customFormat="1">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -520,7 +544,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" s="1" customFormat="1">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -541,6 +565,34 @@
       </c>
       <c r="K3" s="1" t="s">
         <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/XmlData/Datas/__tables__.xlsx
+++ b/XmlData/Datas/__tables__.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yinya\Documents\unityProjects\GGJ2026\XmlData\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCAB9371-EAEE-4DE4-BD2B-DAC07DB7AFC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17D72B77-E1E4-4414-A9BD-687C56AA39D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25710" yWindow="-1210" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
   <si>
     <t>##var</t>
   </si>
@@ -119,6 +119,15 @@
   </si>
   <si>
     <t>Data.CheeseDictionary</t>
+  </si>
+  <si>
+    <t>Table.TbDialog</t>
+  </si>
+  <si>
+    <t>Data.Dialog</t>
+  </si>
+  <si>
+    <t>Dialog.xlsx</t>
   </si>
 </sst>
 </file>
@@ -461,7 +470,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.7109375" bestFit="1" customWidth="1"/>
@@ -595,6 +604,20 @@
         <v>31</v>
       </c>
     </row>
+    <row r="6" spans="1:11">
+      <c r="B6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
